--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0917CE8-AE5F-45EE-89F9-3D12D5AE14D3}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F14BD334-306E-456D-A0E5-B0C5F4E3E279}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asistencia" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Examen 1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Examen 1'!$A$1:$Z$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Examen 1'!$A$1:$Z$28</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="307">
   <si>
     <t>LISTA DE ASISTENCIA — ARQUITECTURA DE SISTEMAS DE SEGURIDAD  |  Ciclo 2026-A  |  CRN 236396  |  Sección 401  |  Aula 101 Edif. 4L</t>
   </si>
@@ -482,12 +482,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Examen 1</t>
   </si>
   <si>
     <t>Examen 2</t>
@@ -993,6 +987,18 @@
   </si>
   <si>
     <t>PIMENTEL MELGOZA ISRAEL RICARDO</t>
+  </si>
+  <si>
+    <t>emmanuel.deluna1544@alumnos.udg.mx</t>
+  </si>
+  <si>
+    <t>101 / 110</t>
+  </si>
+  <si>
+    <t>confiablidad, se extrajeron datos se extrajo información sin que hubiera controles que lo impidieran o detectaran , porque tenia privilegios mínimos para acceder a ellos sin una autorización mayor o del alguien mas, usar controls cis superiores porque al no tener dichos controles, pueden volver a pasar este tipo de situaciones las cuales solo provocara la desconfianza del cliente y al implementar dichos controles le ayudaran mitigar</t>
+  </si>
+  <si>
+    <t>DE LUNA MOZQUEDA EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1008,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,8 +1096,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1184,12 +1196,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFF2F7F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5B3F86"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1213,7 +1219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1250,219 +1256,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF5B3F86"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF5B3F86"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF442F65"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF5B3F86"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF442F65"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFF8F9FA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF442F65"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1470,7 +1274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1544,28 +1348,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1574,80 +1367,56 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="11" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="11" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="22" fontId="11" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1955,15 +1724,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP35"/>
+  <dimension ref="A1:AO35"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" customWidth="1"/>
     <col min="7" max="17" width="4.42578125" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
     <col min="19" max="32" width="4.42578125" customWidth="1"/>
@@ -1974,94 +1743,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
     </row>
     <row r="2" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="29"/>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="29"/>
+      <c r="AM2" s="29"/>
+      <c r="AN2" s="29"/>
+      <c r="AO2" s="29"/>
     </row>
     <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2077,75 +1846,75 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G3" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="33" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="34" t="s">
+      <c r="J3" s="31"/>
+      <c r="K3" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="34"/>
-      <c r="M3" s="33" t="s">
+      <c r="L3" s="30"/>
+      <c r="M3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="33"/>
-      <c r="O3" s="34" t="s">
+      <c r="N3" s="31"/>
+      <c r="O3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="33" t="s">
+      <c r="P3" s="30"/>
+      <c r="Q3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="33"/>
-      <c r="S3" s="34" t="s">
+      <c r="R3" s="31"/>
+      <c r="S3" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="34"/>
-      <c r="U3" s="33" t="s">
+      <c r="T3" s="30"/>
+      <c r="U3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="33"/>
-      <c r="W3" s="34" t="s">
+      <c r="V3" s="31"/>
+      <c r="W3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="33" t="s">
+      <c r="X3" s="30"/>
+      <c r="Y3" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="34" t="s">
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="34"/>
-      <c r="AC3" s="33" t="s">
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="34" t="s">
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="33" t="s">
+      <c r="AF3" s="30"/>
+      <c r="AG3" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="AH3" s="33"/>
-      <c r="AI3" s="34" t="s">
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="33" t="s">
+      <c r="AJ3" s="30"/>
+      <c r="AK3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="33"/>
+      <c r="AL3" s="31"/>
       <c r="AM3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2460,7 +2229,9 @@
       <c r="AD6" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE6" s="12"/>
+      <c r="AE6" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF6" s="12"/>
       <c r="AG6" s="23"/>
       <c r="AH6" s="12"/>
@@ -2470,7 +2241,7 @@
       <c r="AL6" s="12"/>
       <c r="AM6" s="13">
         <f t="shared" ref="AM6:AM32" si="0">COUNTIF(G6,"A")+COUNTIF(H6,"A")+COUNTIF(I6,"A")+COUNTIF(J6,"A")+COUNTIF(K6,"A")+COUNTIF(L6,"A")+COUNTIF(M6,"A")+COUNTIF(N6,"A")+COUNTIF(O6,"A")+COUNTIF(P6,"A")+COUNTIF(Q6,"A")+COUNTIF(R6,"A")+COUNTIF(S6,"A")+COUNTIF(T6,"A")+COUNTIF(U6,"A")+COUNTIF(V6,"A")+COUNTIF(W6,"A")+COUNTIF(X6,"A")+COUNTIF(Y6,"A")+COUNTIF(Z6,"A")+COUNTIF(AA6,"A")+COUNTIF(AB6,"A")+COUNTIF(AC6,"A")+COUNTIF(AD6,"A")+COUNTIF(AE6,"A")+COUNTIF(AF6,"A")+COUNTIF(AG6,"A")+COUNTIF(AH6,"A")+COUNTIF(AI6,"A")+COUNTIF(AJ6,"A")+COUNTIF(AK6,"A")+COUNTIF(AL6,"A")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN6" s="14">
         <f t="shared" ref="AN6:AN32" si="1">COUNTIF(G6,"F")+COUNTIF(H6,"F")+COUNTIF(I6,"F")+COUNTIF(J6,"F")+COUNTIF(K6,"F")+COUNTIF(L6,"F")+COUNTIF(M6,"F")+COUNTIF(N6,"F")+COUNTIF(O6,"F")+COUNTIF(P6,"F")+COUNTIF(Q6,"F")+COUNTIF(R6,"F")+COUNTIF(S6,"F")+COUNTIF(T6,"F")+COUNTIF(U6,"F")+COUNTIF(V6,"F")+COUNTIF(W6,"F")+COUNTIF(X6,"F")+COUNTIF(Y6,"F")+COUNTIF(Z6,"F")+COUNTIF(AA6,"F")+COUNTIF(AB6,"F")+COUNTIF(AC6,"F")+COUNTIF(AD6,"F")+COUNTIF(AE6,"F")+COUNTIF(AF6,"F")+COUNTIF(AG6,"F")+COUNTIF(AH6,"F")+COUNTIF(AI6,"F")+COUNTIF(AJ6,"F")+COUNTIF(AK6,"F")+COUNTIF(AL6,"F")</f>
@@ -2478,7 +2249,7 @@
       </c>
       <c r="AO6" s="15">
         <f t="shared" ref="AO6:AO32" si="2">IF(AM6=0,"",AM6/32)</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2571,7 +2342,9 @@
       <c r="AD7" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="19"/>
+      <c r="AE7" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF7" s="19"/>
       <c r="AG7" s="24"/>
       <c r="AH7" s="19"/>
@@ -2581,7 +2354,7 @@
       <c r="AL7" s="19"/>
       <c r="AM7" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN7" s="14">
         <f t="shared" si="1"/>
@@ -2589,7 +2362,7 @@
       </c>
       <c r="AO7" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="8" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2684,7 +2457,9 @@
       <c r="AD8" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE8" s="12"/>
+      <c r="AE8" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF8" s="12"/>
       <c r="AG8" s="23"/>
       <c r="AH8" s="12"/>
@@ -2694,7 +2469,7 @@
       <c r="AL8" s="12"/>
       <c r="AM8" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN8" s="14">
         <f t="shared" si="1"/>
@@ -2702,7 +2477,7 @@
       </c>
       <c r="AO8" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2795,7 +2570,9 @@
       <c r="AD9" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE9" s="19"/>
+      <c r="AE9" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF9" s="19"/>
       <c r="AG9" s="24"/>
       <c r="AH9" s="19"/>
@@ -2805,7 +2582,7 @@
       <c r="AL9" s="19"/>
       <c r="AM9" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN9" s="14">
         <f t="shared" si="1"/>
@@ -2813,7 +2590,7 @@
       </c>
       <c r="AO9" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2908,7 +2685,9 @@
       <c r="AD10" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE10" s="12"/>
+      <c r="AE10" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF10" s="12"/>
       <c r="AG10" s="23"/>
       <c r="AH10" s="12"/>
@@ -2918,7 +2697,7 @@
       <c r="AL10" s="12"/>
       <c r="AM10" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN10" s="14">
         <f t="shared" si="1"/>
@@ -2926,7 +2705,7 @@
       </c>
       <c r="AO10" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="11" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2944,8 +2723,8 @@
       </c>
       <c r="E11" s="18"/>
       <c r="F11" s="11">
-        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B11&amp;" "&amp;C11,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
-        <v>0</v>
+        <f>IFERROR(ROUND(_xlfn.XLOOKUP(B11&amp;" "&amp;C11,'Examen 1'!B$2:B$28,'Examen 1'!E$2:E$28,0)/100*5,1),0)</f>
+        <v>5</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>145</v>
@@ -3019,7 +2798,9 @@
       <c r="AD11" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE11" s="19"/>
+      <c r="AE11" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF11" s="19"/>
       <c r="AG11" s="24"/>
       <c r="AH11" s="19"/>
@@ -3029,7 +2810,7 @@
       <c r="AL11" s="19"/>
       <c r="AM11" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN11" s="14">
         <f t="shared" si="1"/>
@@ -3037,7 +2818,7 @@
       </c>
       <c r="AO11" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3132,7 +2913,9 @@
       <c r="AD12" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE12" s="12"/>
+      <c r="AE12" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF12" s="12"/>
       <c r="AG12" s="23"/>
       <c r="AH12" s="12"/>
@@ -3142,7 +2925,7 @@
       <c r="AL12" s="12"/>
       <c r="AM12" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN12" s="14">
         <f t="shared" si="1"/>
@@ -3150,7 +2933,7 @@
       </c>
       <c r="AO12" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3243,7 +3026,9 @@
       <c r="AD13" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE13" s="19"/>
+      <c r="AE13" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF13" s="19"/>
       <c r="AG13" s="24"/>
       <c r="AH13" s="19"/>
@@ -3253,7 +3038,7 @@
       <c r="AL13" s="19"/>
       <c r="AM13" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN13" s="14">
         <f t="shared" si="1"/>
@@ -3261,7 +3046,7 @@
       </c>
       <c r="AO13" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="14" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3354,7 +3139,9 @@
       <c r="AD14" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE14" s="12"/>
+      <c r="AE14" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF14" s="12"/>
       <c r="AG14" s="23"/>
       <c r="AH14" s="12"/>
@@ -3364,7 +3151,7 @@
       <c r="AL14" s="12"/>
       <c r="AM14" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN14" s="14">
         <f t="shared" si="1"/>
@@ -3372,7 +3159,7 @@
       </c>
       <c r="AO14" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="15" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3459,7 +3246,7 @@
         <v>145</v>
       </c>
       <c r="AB15" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AC15" s="12" t="s">
         <v>145</v>
@@ -3467,7 +3254,9 @@
       <c r="AD15" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE15" s="19"/>
+      <c r="AE15" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF15" s="19"/>
       <c r="AG15" s="24"/>
       <c r="AH15" s="19"/>
@@ -3477,15 +3266,15 @@
       <c r="AL15" s="19"/>
       <c r="AM15" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN15" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="15">
         <f t="shared" si="2"/>
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,7 +3367,9 @@
       <c r="AD16" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE16" s="12"/>
+      <c r="AE16" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF16" s="12"/>
       <c r="AG16" s="23"/>
       <c r="AH16" s="12"/>
@@ -3588,7 +3379,7 @@
       <c r="AL16" s="12"/>
       <c r="AM16" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN16" s="14">
         <f t="shared" si="1"/>
@@ -3596,10 +3387,10 @@
       </c>
       <c r="AO16" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>12</v>
       </c>
@@ -3689,7 +3480,9 @@
       <c r="AD17" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE17" s="19"/>
+      <c r="AE17" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF17" s="19"/>
       <c r="AG17" s="24"/>
       <c r="AH17" s="19"/>
@@ -3699,7 +3492,7 @@
       <c r="AL17" s="19"/>
       <c r="AM17" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN17" s="14">
         <f t="shared" si="1"/>
@@ -3707,10 +3500,10 @@
       </c>
       <c r="AO17" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>13</v>
       </c>
@@ -3800,7 +3593,9 @@
       <c r="AD18" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE18" s="12"/>
+      <c r="AE18" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF18" s="12"/>
       <c r="AG18" s="23"/>
       <c r="AH18" s="12"/>
@@ -3810,7 +3605,7 @@
       <c r="AL18" s="12"/>
       <c r="AM18" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN18" s="14">
         <f t="shared" si="1"/>
@@ -3818,10 +3613,10 @@
       </c>
       <c r="AO18" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>14</v>
       </c>
@@ -3913,7 +3708,9 @@
       <c r="AD19" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE19" s="19"/>
+      <c r="AE19" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF19" s="19"/>
       <c r="AG19" s="24"/>
       <c r="AH19" s="19"/>
@@ -3923,7 +3720,7 @@
       <c r="AL19" s="19"/>
       <c r="AM19" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN19" s="14">
         <f t="shared" si="1"/>
@@ -3931,10 +3728,10 @@
       </c>
       <c r="AO19" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>15</v>
       </c>
@@ -4016,7 +3813,7 @@
         <v>145</v>
       </c>
       <c r="AB20" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AC20" s="12" t="s">
         <v>145</v>
@@ -4024,7 +3821,9 @@
       <c r="AD20" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE20" s="12"/>
+      <c r="AE20" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="23"/>
       <c r="AH20" s="12"/>
@@ -4034,132 +3833,131 @@
       <c r="AL20" s="12"/>
       <c r="AM20" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN20" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="15">
         <f t="shared" si="2"/>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="21" spans="1:42" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:41" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
         <v>16</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="11">
+      <c r="E21" s="36"/>
+      <c r="F21" s="36">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B21&amp;" "&amp;C21,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="L21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="M21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="N21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="O21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="P21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="R21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="S21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="T21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="U21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="V21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="W21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="X21" s="24" t="s">
+      <c r="G21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="L21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="M21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="O21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="P21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="R21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="S21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="T21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="U21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="V21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="W21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="X21" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="Y21" s="24" t="s">
+      <c r="Y21" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="Z21" s="24" t="s">
+      <c r="Z21" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="AA21" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB21" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC21" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD21" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="24"/>
-      <c r="AK21" s="24"/>
-      <c r="AL21" s="24"/>
-      <c r="AM21" s="30">
+      <c r="AA21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD21" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE21" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="37"/>
+      <c r="AI21" s="37"/>
+      <c r="AJ21" s="37"/>
+      <c r="AK21" s="37"/>
+      <c r="AL21" s="37"/>
+      <c r="AM21" s="34">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="AN21" s="31">
+        <v>22</v>
+      </c>
+      <c r="AN21" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="32">
+      <c r="AO21" s="38">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-      <c r="AP21" s="26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>17</v>
       </c>
@@ -4241,7 +4039,7 @@
         <v>145</v>
       </c>
       <c r="AB22" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AC22" s="12" t="s">
         <v>145</v>
@@ -4249,7 +4047,9 @@
       <c r="AD22" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE22" s="12"/>
+      <c r="AE22" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF22" s="12"/>
       <c r="AG22" s="23"/>
       <c r="AH22" s="12"/>
@@ -4259,18 +4059,18 @@
       <c r="AL22" s="12"/>
       <c r="AM22" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN22" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" s="15">
         <f t="shared" si="2"/>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="23" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>18</v>
       </c>
@@ -4360,7 +4160,9 @@
       <c r="AD23" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE23" s="19"/>
+      <c r="AE23" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF23" s="19"/>
       <c r="AG23" s="24"/>
       <c r="AH23" s="19"/>
@@ -4370,7 +4172,7 @@
       <c r="AL23" s="19"/>
       <c r="AM23" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN23" s="14">
         <f t="shared" si="1"/>
@@ -4378,10 +4180,10 @@
       </c>
       <c r="AO23" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="24" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>19</v>
       </c>
@@ -4471,7 +4273,9 @@
       <c r="AD24" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE24" s="12"/>
+      <c r="AE24" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="23"/>
       <c r="AH24" s="12"/>
@@ -4481,7 +4285,7 @@
       <c r="AL24" s="12"/>
       <c r="AM24" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN24" s="14">
         <f t="shared" si="1"/>
@@ -4489,10 +4293,10 @@
       </c>
       <c r="AO24" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="25" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>20</v>
       </c>
@@ -4582,7 +4386,9 @@
       <c r="AD25" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE25" s="19"/>
+      <c r="AE25" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF25" s="19"/>
       <c r="AG25" s="24"/>
       <c r="AH25" s="19"/>
@@ -4592,7 +4398,7 @@
       <c r="AL25" s="19"/>
       <c r="AM25" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN25" s="14">
         <f t="shared" si="1"/>
@@ -4600,10 +4406,10 @@
       </c>
       <c r="AO25" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>21</v>
       </c>
@@ -4693,7 +4499,9 @@
       <c r="AD26" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE26" s="12"/>
+      <c r="AE26" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF26" s="12"/>
       <c r="AG26" s="23"/>
       <c r="AH26" s="12"/>
@@ -4703,7 +4511,7 @@
       <c r="AL26" s="12"/>
       <c r="AM26" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN26" s="14">
         <f t="shared" si="1"/>
@@ -4711,10 +4519,10 @@
       </c>
       <c r="AO26" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="27" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>22</v>
       </c>
@@ -4727,7 +4535,9 @@
       <c r="D27" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="18">
+        <v>1</v>
+      </c>
       <c r="F27" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B27&amp;" "&amp;C27,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>3.1</v>
@@ -4804,7 +4614,9 @@
       <c r="AD27" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE27" s="19"/>
+      <c r="AE27" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF27" s="19"/>
       <c r="AG27" s="24"/>
       <c r="AH27" s="19"/>
@@ -4814,7 +4626,7 @@
       <c r="AL27" s="19"/>
       <c r="AM27" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN27" s="14">
         <f t="shared" si="1"/>
@@ -4822,10 +4634,10 @@
       </c>
       <c r="AO27" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>23</v>
       </c>
@@ -4915,7 +4727,9 @@
       <c r="AD28" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE28" s="12"/>
+      <c r="AE28" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF28" s="12"/>
       <c r="AG28" s="23"/>
       <c r="AH28" s="12"/>
@@ -4925,7 +4739,7 @@
       <c r="AL28" s="12"/>
       <c r="AM28" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN28" s="14">
         <f t="shared" si="1"/>
@@ -4933,10 +4747,10 @@
       </c>
       <c r="AO28" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>24</v>
       </c>
@@ -5028,7 +4842,9 @@
       <c r="AD29" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE29" s="19"/>
+      <c r="AE29" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF29" s="19"/>
       <c r="AG29" s="24"/>
       <c r="AH29" s="19"/>
@@ -5038,7 +4854,7 @@
       <c r="AL29" s="19"/>
       <c r="AM29" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN29" s="14">
         <f t="shared" si="1"/>
@@ -5046,10 +4862,10 @@
       </c>
       <c r="AO29" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>25</v>
       </c>
@@ -5141,7 +4957,9 @@
       <c r="AD30" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE30" s="12"/>
+      <c r="AE30" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF30" s="12"/>
       <c r="AG30" s="23"/>
       <c r="AH30" s="12"/>
@@ -5151,7 +4969,7 @@
       <c r="AL30" s="12"/>
       <c r="AM30" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN30" s="14">
         <f t="shared" si="1"/>
@@ -5159,10 +4977,10 @@
       </c>
       <c r="AO30" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>26</v>
       </c>
@@ -5176,7 +4994,7 @@
         <v>136</v>
       </c>
       <c r="E31" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B31&amp;" "&amp;C31,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
@@ -5254,7 +5072,9 @@
       <c r="AD31" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE31" s="19"/>
+      <c r="AE31" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF31" s="19"/>
       <c r="AG31" s="24"/>
       <c r="AH31" s="19"/>
@@ -5264,7 +5084,7 @@
       <c r="AL31" s="19"/>
       <c r="AM31" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN31" s="14">
         <f t="shared" si="1"/>
@@ -5272,10 +5092,10 @@
       </c>
       <c r="AO31" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
-      </c>
-    </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>27</v>
       </c>
@@ -5367,7 +5187,9 @@
       <c r="AD32" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AE32" s="12"/>
+      <c r="AE32" s="12" t="s">
+        <v>145</v>
+      </c>
       <c r="AF32" s="12"/>
       <c r="AG32" s="23"/>
       <c r="AH32" s="12"/>
@@ -5377,7 +5199,7 @@
       <c r="AL32" s="12"/>
       <c r="AM32" s="13">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN32" s="14">
         <f t="shared" si="1"/>
@@ -5385,16 +5207,16 @@
       </c>
       <c r="AO32" s="15">
         <f t="shared" si="2"/>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="33" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="20">
@@ -5483,7 +5305,7 @@
       </c>
       <c r="AB33" s="20">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AC33" s="20">
         <f t="shared" si="3"/>
@@ -5495,7 +5317,7 @@
       </c>
       <c r="AE33" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF33" s="20">
         <f t="shared" si="3"/>
@@ -5530,57 +5352,61 @@
       <c r="AO33" s="5"/>
     </row>
     <row r="34" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="36"/>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="36"/>
-      <c r="AA34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
-      <c r="AE34" s="36"/>
-      <c r="AF34" s="36"/>
-      <c r="AG34" s="36"/>
-      <c r="AH34" s="36"/>
-      <c r="AI34" s="36"/>
-      <c r="AJ34" s="36"/>
-      <c r="AK34" s="36"/>
-      <c r="AL34" s="36"/>
-      <c r="AM34" s="36"/>
-      <c r="AN34" s="36"/>
-      <c r="AO34" s="36"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="33"/>
+      <c r="AJ34" s="33"/>
+      <c r="AK34" s="33"/>
+      <c r="AL34" s="33"/>
+      <c r="AM34" s="33"/>
+      <c r="AN34" s="33"/>
+      <c r="AO34" s="33"/>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="AG35" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A34:AO34"/>
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="A2:AO2"/>
     <mergeCell ref="G3:H3"/>
@@ -5597,10 +5423,6 @@
     <mergeCell ref="AC3:AD3"/>
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A34:AO34"/>
   </mergeCells>
   <conditionalFormatting sqref="AO6:AO32">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5630,16 +5452,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -5682,7 +5504,7 @@
       </c>
       <c r="E3" s="13">
         <f>Asistencia!AM6</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="14">
         <f>Asistencia!AN6</f>
@@ -5690,7 +5512,7 @@
       </c>
       <c r="G3" s="15">
         <f>Asistencia!AO6</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H3" s="9" t="str">
         <f>IF(Asistencia!AO6="","Sin datos",IF(Asistencia!AO6&gt;=0.8,"✅ Asistencia!AB6ARegular","⚠️ En riesgo"))</f>
@@ -5712,7 +5534,7 @@
       </c>
       <c r="E4" s="13">
         <f>Asistencia!AM7</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="14">
         <f>Asistencia!AN7</f>
@@ -5720,7 +5542,7 @@
       </c>
       <c r="G4" s="15">
         <f>Asistencia!AO7</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H4" s="16" t="str">
         <f>IF(Asistencia!AO7="","Sin datos",IF(Asistencia!AO7&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5742,7 +5564,7 @@
       </c>
       <c r="E5" s="13">
         <f>Asistencia!AM8</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="14">
         <f>Asistencia!AN8</f>
@@ -5750,7 +5572,7 @@
       </c>
       <c r="G5" s="15">
         <f>Asistencia!AO8</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H5" s="9" t="str">
         <f>IF(Asistencia!AO8="","Sin datos",IF(Asistencia!AO8&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5772,7 +5594,7 @@
       </c>
       <c r="E6" s="13">
         <f>Asistencia!AM9</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="14">
         <f>Asistencia!AN9</f>
@@ -5780,7 +5602,7 @@
       </c>
       <c r="G6" s="15">
         <f>Asistencia!AO9</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H6" s="16" t="str">
         <f>IF(Asistencia!AO9="","Sin datos",IF(Asistencia!AO9&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5802,7 +5624,7 @@
       </c>
       <c r="E7" s="13">
         <f>Asistencia!AM10</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="14">
         <f>Asistencia!AN10</f>
@@ -5810,7 +5632,7 @@
       </c>
       <c r="G7" s="15">
         <f>Asistencia!AO10</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H7" s="9" t="str">
         <f>IF(Asistencia!AO10="","Sin datos",IF(Asistencia!AO10&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5832,7 +5654,7 @@
       </c>
       <c r="E8" s="13">
         <f>Asistencia!AM11</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="14">
         <f>Asistencia!AN11</f>
@@ -5840,7 +5662,7 @@
       </c>
       <c r="G8" s="15">
         <f>Asistencia!AO11</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H8" s="16" t="str">
         <f>IF(Asistencia!AO11="","Sin datos",IF(Asistencia!AO11&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5862,7 +5684,7 @@
       </c>
       <c r="E9" s="13">
         <f>Asistencia!AM12</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="14">
         <f>Asistencia!AN12</f>
@@ -5870,7 +5692,7 @@
       </c>
       <c r="G9" s="15">
         <f>Asistencia!AO12</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H9" s="9" t="str">
         <f>IF(Asistencia!AO12="","Sin datos",IF(Asistencia!AO12&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5892,7 +5714,7 @@
       </c>
       <c r="E10" s="13">
         <f>Asistencia!AM13</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="14">
         <f>Asistencia!AN13</f>
@@ -5900,7 +5722,7 @@
       </c>
       <c r="G10" s="15">
         <f>Asistencia!AO13</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H10" s="16" t="str">
         <f>IF(Asistencia!AO13="","Sin datos",IF(Asistencia!AO13&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5922,7 +5744,7 @@
       </c>
       <c r="E11" s="13">
         <f>Asistencia!AM14</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="14">
         <f>Asistencia!AN14</f>
@@ -5930,7 +5752,7 @@
       </c>
       <c r="G11" s="15">
         <f>Asistencia!AO14</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H11" s="9" t="str">
         <f>IF(Asistencia!AO14="","Sin datos",IF(Asistencia!AO14&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5952,15 +5774,15 @@
       </c>
       <c r="E12" s="13">
         <f>Asistencia!AM15</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F12" s="14">
         <f>Asistencia!AN15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="15">
         <f>Asistencia!AO15</f>
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="H12" s="16" t="str">
         <f>IF(Asistencia!AO15="","Sin datos",IF(Asistencia!AO15&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -5982,7 +5804,7 @@
       </c>
       <c r="E13" s="13">
         <f>Asistencia!AM16</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="14">
         <f>Asistencia!AN16</f>
@@ -5990,7 +5812,7 @@
       </c>
       <c r="G13" s="15">
         <f>Asistencia!AO16</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H13" s="9" t="str">
         <f>IF(Asistencia!AO16="","Sin datos",IF(Asistencia!AO16&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6012,7 +5834,7 @@
       </c>
       <c r="E14" s="13">
         <f>Asistencia!AM17</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="14">
         <f>Asistencia!AN17</f>
@@ -6020,7 +5842,7 @@
       </c>
       <c r="G14" s="15">
         <f>Asistencia!AO17</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H14" s="16" t="str">
         <f>IF(Asistencia!AO17="","Sin datos",IF(Asistencia!AO17&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6042,7 +5864,7 @@
       </c>
       <c r="E15" s="13">
         <f>Asistencia!AM18</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
         <f>Asistencia!AN18</f>
@@ -6050,7 +5872,7 @@
       </c>
       <c r="G15" s="15">
         <f>Asistencia!AO18</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H15" s="9" t="str">
         <f>IF(Asistencia!AO18="","Sin datos",IF(Asistencia!AO18&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6072,7 +5894,7 @@
       </c>
       <c r="E16" s="13">
         <f>Asistencia!AM19</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="14">
         <f>Asistencia!AN19</f>
@@ -6080,7 +5902,7 @@
       </c>
       <c r="G16" s="15">
         <f>Asistencia!AO19</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H16" s="16" t="str">
         <f>IF(Asistencia!AO19="","Sin datos",IF(Asistencia!AO19&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6102,15 +5924,15 @@
       </c>
       <c r="E17" s="13">
         <f>Asistencia!AM20</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F17" s="14">
         <f>Asistencia!AN20</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15">
         <f>Asistencia!AO20</f>
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="H17" s="9" t="str">
         <f>IF(Asistencia!AO20="","Sin datos",IF(Asistencia!AO20&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6132,7 +5954,7 @@
       </c>
       <c r="E18" s="13">
         <f>Asistencia!AM21</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="14">
         <f>Asistencia!AN21</f>
@@ -6140,7 +5962,7 @@
       </c>
       <c r="G18" s="15">
         <f>Asistencia!AO21</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H18" s="16" t="str">
         <f>IF(Asistencia!AO21="","Sin datos",IF(Asistencia!AO21&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6162,15 +5984,15 @@
       </c>
       <c r="E19" s="13">
         <f>Asistencia!AM22</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F19" s="14">
         <f>Asistencia!AN22</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="15">
         <f>Asistencia!AO22</f>
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="H19" s="9" t="str">
         <f>IF(Asistencia!AO22="","Sin datos",IF(Asistencia!AO22&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6192,7 +6014,7 @@
       </c>
       <c r="E20" s="13">
         <f>Asistencia!AM23</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="14">
         <f>Asistencia!AN23</f>
@@ -6200,7 +6022,7 @@
       </c>
       <c r="G20" s="15">
         <f>Asistencia!AO23</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H20" s="16" t="str">
         <f>IF(Asistencia!AO23="","Sin datos",IF(Asistencia!AO23&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6222,7 +6044,7 @@
       </c>
       <c r="E21" s="13">
         <f>Asistencia!AM24</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="14">
         <f>Asistencia!AN24</f>
@@ -6230,7 +6052,7 @@
       </c>
       <c r="G21" s="15">
         <f>Asistencia!AO24</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H21" s="9" t="str">
         <f>IF(Asistencia!AO24="","Sin datos",IF(Asistencia!AO24&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6252,7 +6074,7 @@
       </c>
       <c r="E22" s="13">
         <f>Asistencia!AM25</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <f>Asistencia!AN25</f>
@@ -6260,7 +6082,7 @@
       </c>
       <c r="G22" s="15">
         <f>Asistencia!AO25</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H22" s="16" t="str">
         <f>IF(Asistencia!AO25="","Sin datos",IF(Asistencia!AO25&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6282,7 +6104,7 @@
       </c>
       <c r="E23" s="13">
         <f>Asistencia!AM26</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="14">
         <f>Asistencia!AN26</f>
@@ -6290,7 +6112,7 @@
       </c>
       <c r="G23" s="15">
         <f>Asistencia!AO26</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H23" s="9" t="str">
         <f>IF(Asistencia!AO26="","Sin datos",IF(Asistencia!AO26&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6312,7 +6134,7 @@
       </c>
       <c r="E24" s="13">
         <f>Asistencia!AM27</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24" s="14">
         <f>Asistencia!AN27</f>
@@ -6320,7 +6142,7 @@
       </c>
       <c r="G24" s="15">
         <f>Asistencia!AO27</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H24" s="16" t="str">
         <f>IF(Asistencia!AO27="","Sin datos",IF(Asistencia!AO27&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6342,7 +6164,7 @@
       </c>
       <c r="E25" s="13">
         <f>Asistencia!AM28</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="14">
         <f>Asistencia!AN28</f>
@@ -6350,7 +6172,7 @@
       </c>
       <c r="G25" s="15">
         <f>Asistencia!AO28</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H25" s="9" t="str">
         <f>IF(Asistencia!AO28="","Sin datos",IF(Asistencia!AO28&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6372,7 +6194,7 @@
       </c>
       <c r="E26" s="13">
         <f>Asistencia!AM29</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" s="14">
         <f>Asistencia!AN29</f>
@@ -6380,7 +6202,7 @@
       </c>
       <c r="G26" s="15">
         <f>Asistencia!AO29</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H26" s="16" t="str">
         <f>IF(Asistencia!AO29="","Sin datos",IF(Asistencia!AO29&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6402,7 +6224,7 @@
       </c>
       <c r="E27" s="13">
         <f>Asistencia!AM30</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
         <f>Asistencia!AN30</f>
@@ -6410,7 +6232,7 @@
       </c>
       <c r="G27" s="15">
         <f>Asistencia!AO30</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H27" s="9" t="str">
         <f>IF(Asistencia!AO30="","Sin datos",IF(Asistencia!AO30&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6432,7 +6254,7 @@
       </c>
       <c r="E28" s="13">
         <f>Asistencia!AM31</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F28" s="14">
         <f>Asistencia!AN31</f>
@@ -6440,7 +6262,7 @@
       </c>
       <c r="G28" s="15">
         <f>Asistencia!AO31</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H28" s="16" t="str">
         <f>IF(Asistencia!AO31="","Sin datos",IF(Asistencia!AO31&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6462,7 +6284,7 @@
       </c>
       <c r="E29" s="13">
         <f>Asistencia!AM32</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
         <f>Asistencia!AN32</f>
@@ -6470,7 +6292,7 @@
       </c>
       <c r="G29" s="15">
         <f>Asistencia!AO32</f>
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="H29" s="9" t="str">
         <f>IF(Asistencia!AO32="","Sin datos",IF(Asistencia!AO32&gt;=0.8,"✅ Regular","⚠️ En riesgo"))</f>
@@ -6488,2210 +6310,2285 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B781B1C-465B-40C3-B31E-0122F766D036}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="57" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="58" t="s">
-        <v>278</v>
-      </c>
-      <c r="C1" s="40" t="s">
+      <c r="F1" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="40" t="s">
-        <v>275</v>
-      </c>
-      <c r="E1" s="55" t="s">
+      <c r="G1" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="H1" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="I1" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="J1" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="K1" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="40" t="s">
+      <c r="L1" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="M1" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="40" t="s">
+      <c r="N1" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="40" t="s">
+      <c r="O1" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="P1" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="Q1" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="P1" s="40" t="s">
+      <c r="R1" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="Q1" s="40" t="s">
+      <c r="S1" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="T1" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="S1" s="40" t="s">
+      <c r="U1" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="T1" s="40" t="s">
+      <c r="V1" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="U1" s="40" t="s">
+      <c r="W1" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="X1" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="W1" s="40" t="s">
+      <c r="Y1" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="X1" s="40" t="s">
+      <c r="Z1" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="Y1" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z1" s="41" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="43">
         <v>46106.414525462962</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="E2" s="56">
+      <c r="B2" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="46">
         <f>MIN(100,VALUE(TRIM(LEFT(D2,FIND("/",D2)-1))))</f>
         <v>94</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="I2" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K2" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="L2" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I2" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J2" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K2" s="47" t="s">
+      <c r="M2" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="N2" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="O2" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="P2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="V2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="W2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X2" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y2" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z2" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="O2" s="47" t="s">
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="47">
+        <v>46106.414560185185</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="P2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T2" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="V2" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="W2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X2" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y2" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z2" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42">
-        <v>46106.414560185185</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="C3" s="43" t="s">
+      <c r="E3" s="46">
+        <f t="shared" ref="E3:E28" si="0">MIN(100,VALUE(TRIM(LEFT(D3,FIND("/",D3)-1))))</f>
+        <v>100</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="H3" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K3" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L3" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="M3" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="O3" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="P3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q3" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T3" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U3" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X3" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y3" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z3" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="56">
-        <f t="shared" ref="E3:E27" si="0">MIN(100,VALUE(TRIM(LEFT(D3,FIND("/",D3)-1))))</f>
-        <v>100</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" s="43" t="s">
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>46106.41511574074</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="H3" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K3" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="L3" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="M3" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="N3" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O3" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q3" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T3" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U3" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X3" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y3" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z3" s="45" t="s">
+      <c r="D4" s="45" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="46">
-        <v>46106.41511574074</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="56">
+      <c r="E4" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H4" s="47" t="s">
+      <c r="I4" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K4" s="47" t="s">
+      <c r="M4" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L4" s="47" t="s">
+      <c r="N4" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M4" s="47" t="s">
+      <c r="O4" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N4" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q4" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T4" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U4" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X4" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y4" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z4" s="49" t="s">
+      <c r="P4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z4" s="44" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>46106.416435185187</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42">
-        <v>46106.416435185187</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>282</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="56">
+      <c r="E5" s="46">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G5" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H5" s="43" t="s">
+      <c r="I5" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J5" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="K5" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="L5" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I5" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J5" s="43" t="s">
+      <c r="M5" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="N5" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="O5" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="P5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q5" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T5" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="V5" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="W5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X5" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y5" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z5" s="48" t="s">
         <v>202</v>
       </c>
-      <c r="K5" s="43" t="s">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>46106.416608796295</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="L5" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="M5" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="N5" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O5" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q5" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T5" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="V5" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X5" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y5" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z5" s="45" t="s">
+      <c r="D6" s="45" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46">
-        <v>46106.416608796295</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="E6" s="56">
+      <c r="E6" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G6" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H6" s="47" t="s">
+      <c r="I6" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L6" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I6" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J6" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="K6" s="47" t="s">
+      <c r="M6" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="N6" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M6" s="47" t="s">
+      <c r="O6" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N6" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O6" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q6" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T6" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U6" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X6" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y6" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z6" s="49" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
+      <c r="P6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T6" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U6" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X6" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y6" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z6" s="44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="47">
         <v>46106.417118055557</v>
       </c>
-      <c r="B7" s="60" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" s="56">
+      <c r="B7" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H7" s="43" t="s">
+      <c r="I7" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L7" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I7" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K7" s="43" t="s">
+      <c r="M7" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="N7" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M7" s="43" t="s">
+      <c r="O7" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N7" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O7" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q7" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T7" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U7" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X7" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y7" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z7" s="45" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46">
+      <c r="P7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q7" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T7" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U7" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X7" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y7" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z7" s="48" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
         <v>46106.417129629626</v>
       </c>
-      <c r="B8" s="59" t="s">
-        <v>285</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="56">
+      <c r="B8" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H8" s="47" t="s">
+      <c r="I8" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L8" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I8" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J8" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K8" s="47" t="s">
+      <c r="M8" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L8" s="47" t="s">
+      <c r="N8" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M8" s="47" t="s">
+      <c r="O8" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N8" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O8" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q8" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T8" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U8" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X8" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y8" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z8" s="49" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42">
+      <c r="P8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T8" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U8" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X8" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y8" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z8" s="44" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="47">
         <v>46106.417349537034</v>
       </c>
-      <c r="B9" s="60" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E9" s="56">
+      <c r="B9" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G9" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H9" s="43" t="s">
+      <c r="I9" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J9" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K9" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L9" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I9" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J9" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K9" s="43" t="s">
+      <c r="M9" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L9" s="43" t="s">
+      <c r="N9" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M9" s="43" t="s">
+      <c r="O9" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N9" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O9" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q9" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T9" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U9" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X9" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y9" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z9" s="45" t="s">
+      <c r="P9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q9" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T9" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U9" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X9" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z9" s="48" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>46106.418194444443</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46">
-        <v>46106.418194444443</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="56">
+      <c r="E10" s="46">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H10" s="47" t="s">
+      <c r="I10" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="L10" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I10" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J10" s="47" t="s">
+      <c r="M10" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="O10" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="U10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="V10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X10" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z10" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="K10" s="47" t="s">
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
+        <v>46106.418958333335</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="L10" s="47" t="s">
-        <v>188</v>
-      </c>
-      <c r="M10" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="N10" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O10" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q10" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="U10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="V10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X10" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y10" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z10" s="49" t="s">
+      <c r="D11" s="49" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="42">
-        <v>46106.418958333335</v>
-      </c>
-      <c r="B11" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="56">
+      <c r="E11" s="46">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H11" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G11" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H11" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J11" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K11" s="43" t="s">
+      <c r="I11" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K11" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="M11" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L11" s="43" t="s">
+      <c r="N11" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="O11" s="48" t="s">
+        <v>189</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T11" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="V11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X11" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y11" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z11" s="48" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>46106.418981481482</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="M11" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="N11" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O11" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q11" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T11" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="V11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X11" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y11" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z11" s="45" t="s">
+      <c r="D12" s="45" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46">
-        <v>46106.418981481482</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="E12" s="56">
+      <c r="E12" s="46">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="F12" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="G12" s="47" t="s">
+      <c r="F12" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="N12" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="O12" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="P12" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="S12" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="W12" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X12" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y12" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z12" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="H12" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="47" t="s">
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
+        <v>46106.419062499997</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="J12" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="L12" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="M12" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="N12" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="O12" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P12" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="S12" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="W12" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y12" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z12" s="49" t="s">
+      <c r="D13" s="49" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42">
-        <v>46106.419062499997</v>
-      </c>
-      <c r="B13" s="60" t="s">
-        <v>290</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="E13" s="56">
+      <c r="E13" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F13" s="43" t="s">
+      <c r="F13" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H13" s="43" t="s">
+      <c r="I13" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K13" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L13" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I13" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J13" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K13" s="43" t="s">
+      <c r="M13" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L13" s="43" t="s">
+      <c r="N13" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M13" s="43" t="s">
+      <c r="O13" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N13" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O13" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q13" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="U13" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X13" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y13" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z13" s="45" t="s">
+      <c r="P13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="U13" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X13" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y13" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z13" s="48" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" s="44" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
+      <c r="D14" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="61" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="E14" s="56">
+      <c r="E14" s="46">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="N14" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="O14" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="G14" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="I14" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="J14" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="L14" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="M14" s="47" t="s">
+      <c r="P14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q14" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S14" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="T14" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="W14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X14" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y14" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z14" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="N14" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O14" s="47" t="s">
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="47">
+        <v>46106.419988425929</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="P14" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R14" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="T14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U14" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="V14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="W14" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y14" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z14" s="49" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42">
-        <v>46106.419988425929</v>
-      </c>
-      <c r="B15" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="56">
+      <c r="D15" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F15" s="43" t="s">
+      <c r="F15" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H15" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G15" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H15" s="43" t="s">
+      <c r="I15" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J15" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L15" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I15" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J15" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K15" s="43" t="s">
+      <c r="M15" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L15" s="43" t="s">
+      <c r="N15" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M15" s="43" t="s">
+      <c r="O15" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N15" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O15" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q15" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T15" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U15" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X15" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y15" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z15" s="45" t="s">
+      <c r="P15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q15" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T15" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U15" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X15" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y15" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z15" s="48" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
+        <v>46106.420046296298</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="45" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46">
-        <v>46106.420046296298</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>293</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="E16" s="56">
+      <c r="E16" s="46">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="H16" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G16" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="H16" s="47" t="s">
+      <c r="I16" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L16" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I16" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J16" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K16" s="47" t="s">
+      <c r="M16" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L16" s="47" t="s">
+      <c r="N16" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M16" s="47" t="s">
+      <c r="O16" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N16" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O16" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q16" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="U16" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V16" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="W16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y16" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z16" s="49" t="s">
+      <c r="P16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="U16" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V16" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="W16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y16" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" s="47">
+        <v>46106.420104166667</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="49" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42">
-        <v>46106.420104166667</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="D17" s="44" t="s">
-        <v>244</v>
-      </c>
-      <c r="E17" s="56">
+      <c r="E17" s="46">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="H17" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G17" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="H17" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="I17" s="43" t="s">
+      <c r="I17" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="K17" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="M17" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="N17" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="O17" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="P17" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="S17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="T17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="W17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="X17" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y17" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z17" s="48" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18" s="43">
+        <v>46106.420347222222</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="J17" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="K17" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="L17" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="M17" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="N17" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O17" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="P17" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="S17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="T17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="X17" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y17" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z17" s="45" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46">
-        <v>46106.420347222222</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>295</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="E18" s="56">
+      <c r="D18" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G18" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H18" s="47" t="s">
+      <c r="I18" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L18" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I18" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J18" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K18" s="47" t="s">
+      <c r="M18" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L18" s="47" t="s">
+      <c r="N18" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M18" s="47" t="s">
+      <c r="O18" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N18" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O18" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q18" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T18" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U18" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X18" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y18" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z18" s="49" t="s">
+      <c r="P18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T18" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U18" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X18" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y18" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z18" s="44" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="47">
+        <v>46106.42046296296</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="49" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42">
-        <v>46106.42046296296</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>296</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>249</v>
-      </c>
-      <c r="D19" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="E19" s="56">
+      <c r="E19" s="46">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H19" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G19" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H19" s="43" t="s">
+      <c r="I19" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K19" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I19" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J19" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K19" s="43" t="s">
+      <c r="M19" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L19" s="43" t="s">
+      <c r="N19" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M19" s="43" t="s">
+      <c r="O19" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N19" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O19" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="S19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="T19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="U19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X19" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y19" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z19" s="45" t="s">
+      <c r="P19" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q19" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R19" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="S19" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="T19" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="U19" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V19" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W19" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X19" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y19" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z19" s="48" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="44" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>297</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="E20" s="56">
+      <c r="D20" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H20" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G20" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H20" s="47" t="s">
+      <c r="I20" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K20" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J20" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K20" s="47" t="s">
+      <c r="M20" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L20" s="47" t="s">
+      <c r="N20" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M20" s="47" t="s">
+      <c r="O20" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N20" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O20" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q20" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T20" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U20" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X20" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y20" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z20" s="49" t="s">
+      <c r="P20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T20" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U20" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X20" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y20" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z20" s="44" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" s="47">
+        <v>46106.421365740738</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="D21" s="49" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42">
-        <v>46106.421365740738</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>298</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="44" t="s">
-        <v>256</v>
-      </c>
-      <c r="E21" s="56">
+      <c r="E21" s="46">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G21" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H21" s="43" t="s">
+      <c r="I21" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="K21" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="L21" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I21" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J21" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="L21" s="43" t="s">
+      <c r="M21" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="N21" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M21" s="43" t="s">
+      <c r="O21" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N21" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O21" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q21" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R21" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="S21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="U21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="V21" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="W21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y21" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z21" s="45" t="s">
+      <c r="P21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q21" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R21" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="S21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="U21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="V21" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="W21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y21" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z21" s="48" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" s="43">
+        <v>46106.422662037039</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="D22" s="45" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46">
-        <v>46106.422662037039</v>
-      </c>
-      <c r="B22" s="59" t="s">
-        <v>299</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>259</v>
-      </c>
-      <c r="E22" s="56">
+      <c r="E22" s="46">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G22" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="I22" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="J22" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="L22" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="M22" s="47" t="s">
+      <c r="I22" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K22" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="L22" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="M22" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="N22" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="O22" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N22" s="47" t="s">
+      <c r="P22" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q22" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R22" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S22" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T22" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U22" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="V22" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="W22" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="X22" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y22" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z22" s="44" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="47">
+        <v>46106.42291666667</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="O22" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P22" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q22" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R22" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S22" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T22" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U22" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="V22" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="W22" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="X22" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y22" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z22" s="49" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42">
-        <v>46106.42291666667</v>
-      </c>
-      <c r="B23" s="60" t="s">
-        <v>300</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="D23" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E23" s="56">
+      <c r="D23" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="E23" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H23" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H23" s="43" t="s">
+      <c r="I23" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K23" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L23" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I23" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J23" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K23" s="43" t="s">
+      <c r="M23" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L23" s="43" t="s">
+      <c r="N23" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M23" s="43" t="s">
+      <c r="O23" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N23" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O23" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y23" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z23" s="45" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="46">
+      <c r="P23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q23" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T23" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U23" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X23" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y23" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z23" s="48" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" s="43">
         <v>46106.423321759263</v>
       </c>
-      <c r="B24" s="59" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="56">
+      <c r="B24" s="43" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" s="46">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="F24" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="H24" s="47" t="s">
+      <c r="F24" s="44" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="L24" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I24" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J24" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="L24" s="47" t="s">
+      <c r="M24" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="N24" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M24" s="47" t="s">
+      <c r="O24" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N24" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O24" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q24" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="U24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="V24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X24" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y24" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z24" s="49" t="s">
+      <c r="P24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q24" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="U24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="V24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X24" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y24" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z24" s="44" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" s="47">
+        <v>46106.443576388891</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" s="49" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42">
-        <v>46106.443576388891</v>
-      </c>
-      <c r="B25" s="60" t="s">
-        <v>302</v>
-      </c>
-      <c r="C25" s="43" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="E25" s="56">
+      <c r="E25" s="46">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="F25" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="H25" s="43" t="s">
+      <c r="F25" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H25" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J25" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="43" t="s">
-        <v>176</v>
-      </c>
-      <c r="J25" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="43" t="s">
+      <c r="K25" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L25" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="M25" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L25" s="43" t="s">
+      <c r="N25" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M25" s="43" t="s">
+      <c r="O25" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N25" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="O25" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="P25" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q25" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="R25" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="S25" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="T25" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="U25" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="V25" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="W25" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="X25" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y25" s="43" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z25" s="45" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="46">
+      <c r="P25" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q25" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R25" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S25" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T25" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U25" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V25" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W25" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X25" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y25" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z25" s="48" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="43">
         <v>46106.445543981485</v>
       </c>
-      <c r="B26" s="59" t="s">
-        <v>303</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>250</v>
-      </c>
-      <c r="E26" s="56">
+      <c r="B26" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="E26" s="46">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="H26" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="G26" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="H26" s="47" t="s">
+      <c r="I26" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="K26" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L26" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="I26" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="J26" s="47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K26" s="47" t="s">
+      <c r="M26" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="L26" s="47" t="s">
+      <c r="N26" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M26" s="47" t="s">
+      <c r="O26" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="N26" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="O26" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="P26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q26" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="R26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="S26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="T26" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="U26" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="V26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="W26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="X26" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y26" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z26" s="49" t="s">
+      <c r="P26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q26" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T26" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U26" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X26" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y26" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z26" s="44" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="48" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="51" t="s">
+      <c r="D27" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="B27" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="E27" s="56">
+      <c r="E27" s="46">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F27" s="52" t="s">
+      <c r="F27" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="H27" s="52" t="s">
+      <c r="I27" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="J27" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="K27" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="J27" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="K27" s="52" t="s">
+      <c r="M27" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="L27" s="52" t="s">
+      <c r="N27" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M27" s="52" t="s">
+      <c r="O27" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="N27" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="O27" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="P27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q27" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="R27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="S27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="T27" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="U27" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="V27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="W27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="X27" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y27" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z27" s="54" t="s">
-        <v>274</v>
+      <c r="P27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q27" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="S27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="T27" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="U27" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="V27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="W27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="X27" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y27" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z27" s="48" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A28" s="43">
+        <v>46139.668900462966</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="E28" s="46">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="L28" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="N28" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="P28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q28" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="R28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="S28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="T28" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="U28" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="V28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="W28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="X28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y28" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z28" s="44" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z27" xr:uid="{5B781B1C-465B-40C3-B31E-0122F766D036}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="HERNANDEZ VILLANUEVA VICTOR DANIEL"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:Z28" xr:uid="{5B781B1C-465B-40C3-B31E-0122F766D036}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:Z27">
       <sortCondition descending="1" ref="B1:B27"/>
     </sortState>

--- a/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
+++ b/Administracion/Lista_Asistencia_ASS_CRN236396.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ddf5fb2bc65e958/Documentos/GitHub/lc_arquitectura_de_sistemas_de_seguridad/Administracion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F14BD334-306E-456D-A0E5-B0C5F4E3E279}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="14_{545CCF96-C524-4C47-965E-B405D4770607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56960807-9F25-4073-AF78-1FEDF67E0AE4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1274,7 +1274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1349,40 +1349,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1418,6 +1399,24 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1743,94 +1742,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="28"/>
-      <c r="AM1" s="28"/>
-      <c r="AN1" s="28"/>
-      <c r="AO1" s="28"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="49"/>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
     </row>
     <row r="2" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="29"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="29"/>
-      <c r="AN2" s="29"/>
-      <c r="AO2" s="29"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="50"/>
     </row>
     <row r="3" spans="1:41" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1851,70 +1850,70 @@
       <c r="F3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="31" t="s">
+      <c r="H3" s="45"/>
+      <c r="I3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="30" t="s">
+      <c r="J3" s="46"/>
+      <c r="K3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="31" t="s">
+      <c r="L3" s="45"/>
+      <c r="M3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="31"/>
-      <c r="O3" s="30" t="s">
+      <c r="N3" s="46"/>
+      <c r="O3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="31" t="s">
+      <c r="P3" s="45"/>
+      <c r="Q3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="31"/>
-      <c r="S3" s="30" t="s">
+      <c r="R3" s="46"/>
+      <c r="S3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="30"/>
-      <c r="U3" s="31" t="s">
+      <c r="T3" s="45"/>
+      <c r="U3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="V3" s="31"/>
-      <c r="W3" s="30" t="s">
+      <c r="V3" s="46"/>
+      <c r="W3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="31" t="s">
+      <c r="X3" s="45"/>
+      <c r="Y3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="30" t="s">
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="31" t="s">
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="30" t="s">
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="AF3" s="30"/>
-      <c r="AG3" s="31" t="s">
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="30" t="s">
+      <c r="AH3" s="46"/>
+      <c r="AI3" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="AJ3" s="30"/>
-      <c r="AK3" s="31" t="s">
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AL3" s="31"/>
+      <c r="AL3" s="46"/>
       <c r="AM3" s="4" t="s">
         <v>22</v>
       </c>
@@ -2607,7 +2606,7 @@
         <v>73</v>
       </c>
       <c r="E10" s="11">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B10&amp;" "&amp;C10,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
@@ -3844,115 +3843,115 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="21" spans="1:41" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
+    <row r="21" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28">
         <v>16</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36">
+      <c r="E21" s="30"/>
+      <c r="F21" s="30">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B21&amp;" "&amp;C21,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
         <v>5</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="L21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="M21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="N21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="O21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="P21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="R21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="S21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="T21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="U21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="V21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="W21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="X21" s="37" t="s">
+      <c r="G21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="M21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="N21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="O21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="P21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="R21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="S21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="T21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="U21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="V21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="W21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="X21" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="Y21" s="37" t="s">
+      <c r="Y21" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="Z21" s="37" t="s">
+      <c r="Z21" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="AA21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="AC21" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="AD21" s="37" t="s">
+      <c r="AA21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC21" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD21" s="31" t="s">
         <v>145</v>
       </c>
       <c r="AE21" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="AF21" s="37"/>
-      <c r="AG21" s="40"/>
-      <c r="AH21" s="37"/>
-      <c r="AI21" s="37"/>
-      <c r="AJ21" s="37"/>
-      <c r="AK21" s="37"/>
-      <c r="AL21" s="37"/>
-      <c r="AM21" s="34">
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="33"/>
+      <c r="AH21" s="31"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="31"/>
+      <c r="AK21" s="31"/>
+      <c r="AL21" s="31"/>
+      <c r="AM21" s="28">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AN21" s="34">
+      <c r="AN21" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="38">
+      <c r="AO21" s="32">
         <f t="shared" si="2"/>
         <v>0.6875</v>
       </c>
@@ -4536,7 +4535,7 @@
         <v>124</v>
       </c>
       <c r="E27" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B27&amp;" "&amp;C27,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
@@ -4764,7 +4763,7 @@
         <v>130</v>
       </c>
       <c r="E29" s="18">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F29" s="11">
         <f>IFERROR(ROUND(_xlfn.XLOOKUP(B29&amp;" "&amp;C29,'Examen 1'!B$2:B$27,'Examen 1'!E$2:E$27,0)/100*5,1),0)</f>
@@ -5211,12 +5210,12 @@
       </c>
     </row>
     <row r="33" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="20">
@@ -5352,49 +5351,49 @@
       <c r="AO33" s="5"/>
     </row>
     <row r="34" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
+      <c r="A34" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
-      <c r="AK34" s="33"/>
-      <c r="AL34" s="33"/>
-      <c r="AM34" s="33"/>
-      <c r="AN34" s="33"/>
-      <c r="AO34" s="33"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
+      <c r="N34" s="48"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="48"/>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="48"/>
+      <c r="V34" s="48"/>
+      <c r="W34" s="48"/>
+      <c r="X34" s="48"/>
+      <c r="Y34" s="48"/>
+      <c r="Z34" s="48"/>
+      <c r="AA34" s="48"/>
+      <c r="AB34" s="48"/>
+      <c r="AC34" s="48"/>
+      <c r="AD34" s="48"/>
+      <c r="AE34" s="48"/>
+      <c r="AF34" s="48"/>
+      <c r="AG34" s="48"/>
+      <c r="AH34" s="48"/>
+      <c r="AI34" s="48"/>
+      <c r="AJ34" s="48"/>
+      <c r="AK34" s="48"/>
+      <c r="AL34" s="48"/>
+      <c r="AM34" s="48"/>
+      <c r="AN34" s="48"/>
+      <c r="AO34" s="48"/>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="AG35" s="26" t="s">
@@ -5403,6 +5402,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
     <mergeCell ref="AI3:AJ3"/>
     <mergeCell ref="AK3:AL3"/>
     <mergeCell ref="A33:D33"/>
@@ -5419,10 +5422,6 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
   </mergeCells>
   <conditionalFormatting sqref="AO6:AO32">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5452,16 +5451,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -6321,2269 +6320,2269 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="M1" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="N1" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="O1" s="41" t="s">
+      <c r="O1" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="P1" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="Q1" s="41" t="s">
+      <c r="Q1" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="T1" s="41" t="s">
+      <c r="T1" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="U1" s="41" t="s">
+      <c r="U1" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="V1" s="41" t="s">
+      <c r="V1" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="W1" s="41" t="s">
+      <c r="W1" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="X1" s="41" t="s">
+      <c r="X1" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="Y1" s="41" t="s">
+      <c r="Y1" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="Z1" s="41" t="s">
+      <c r="Z1" s="34" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="36">
         <v>46106.414525462962</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="39">
         <f>MIN(100,VALUE(TRIM(LEFT(D2,FIND("/",D2)-1))))</f>
         <v>94</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L2" s="44" t="s">
+      <c r="L2" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O2" s="44" t="s">
+      <c r="O2" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="V2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="W2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y2" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z2" s="44" t="s">
+      <c r="P2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T2" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V2" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="W2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X2" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z2" s="37" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="47">
+      <c r="A3" s="40">
         <v>46106.414560185185</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="39">
         <f t="shared" ref="E3:E28" si="0">MIN(100,VALUE(TRIM(LEFT(D3,FIND("/",D3)-1))))</f>
         <v>100</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="48" t="s">
+      <c r="I3" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J3" s="48" t="s">
+      <c r="J3" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L3" s="48" t="s">
+      <c r="L3" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M3" s="48" t="s">
+      <c r="M3" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N3" s="48" t="s">
+      <c r="N3" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O3" s="48" t="s">
+      <c r="O3" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q3" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U3" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X3" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y3" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z3" s="48" t="s">
+      <c r="P3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q3" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T3" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U3" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X3" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y3" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z3" s="41" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="43">
+      <c r="A4" s="36">
         <v>46106.41511574074</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="44" t="s">
+      <c r="I4" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J4" s="44" t="s">
+      <c r="J4" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K4" s="44" t="s">
+      <c r="K4" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L4" s="44" t="s">
+      <c r="L4" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M4" s="44" t="s">
+      <c r="M4" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N4" s="44" t="s">
+      <c r="N4" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O4" s="44" t="s">
+      <c r="O4" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q4" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T4" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U4" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X4" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y4" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z4" s="44" t="s">
+      <c r="P4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y4" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z4" s="37" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
+      <c r="A5" s="40">
         <v>46106.416435185187</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="39">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I5" s="48" t="s">
+      <c r="I5" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J5" s="48" t="s">
+      <c r="J5" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="K5" s="48" t="s">
+      <c r="K5" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="L5" s="48" t="s">
+      <c r="L5" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M5" s="48" t="s">
+      <c r="M5" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N5" s="48" t="s">
+      <c r="N5" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q5" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T5" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="V5" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="W5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X5" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y5" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z5" s="48" t="s">
+      <c r="P5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="V5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="W5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y5" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z5" s="41" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
+      <c r="A6" s="36">
         <v>46106.416608796295</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="36" t="s">
         <v>281</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="K6" s="44" t="s">
+      <c r="K6" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N6" s="44" t="s">
+      <c r="N6" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O6" s="44" t="s">
+      <c r="O6" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T6" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U6" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X6" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y6" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z6" s="44" t="s">
+      <c r="P6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q6" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T6" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U6" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X6" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y6" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z6" s="37" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
+      <c r="A7" s="40">
         <v>46106.417118055557</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K7" s="48" t="s">
+      <c r="K7" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N7" s="48" t="s">
+      <c r="N7" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O7" s="48" t="s">
+      <c r="O7" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q7" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T7" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U7" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X7" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y7" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z7" s="48" t="s">
+      <c r="P7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T7" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U7" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X7" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y7" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z7" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
+      <c r="A8" s="36">
         <v>46106.417129629626</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I8" s="44" t="s">
+      <c r="I8" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J8" s="44" t="s">
+      <c r="J8" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K8" s="44" t="s">
+      <c r="K8" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L8" s="44" t="s">
+      <c r="L8" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N8" s="44" t="s">
+      <c r="N8" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O8" s="44" t="s">
+      <c r="O8" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T8" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U8" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X8" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y8" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z8" s="44" t="s">
+      <c r="P8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q8" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T8" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U8" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X8" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y8" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z8" s="37" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
+      <c r="A9" s="40">
         <v>46106.417349537034</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L9" s="48" t="s">
+      <c r="L9" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M9" s="48" t="s">
+      <c r="M9" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N9" s="48" t="s">
+      <c r="N9" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O9" s="48" t="s">
+      <c r="O9" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q9" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T9" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U9" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X9" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y9" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z9" s="48" t="s">
+      <c r="P9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q9" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T9" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U9" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X9" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z9" s="41" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="36">
         <v>46106.418194444443</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="36" t="s">
         <v>285</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="39">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="I10" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J10" s="44" t="s">
+      <c r="J10" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M10" s="44" t="s">
+      <c r="M10" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N10" s="44" t="s">
+      <c r="N10" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="O10" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="U10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="V10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X10" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y10" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z10" s="44" t="s">
+      <c r="P10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q10" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="U10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X10" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y10" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z10" s="37" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
+      <c r="A11" s="40">
         <v>46106.418958333335</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="39">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J11" s="48" t="s">
+      <c r="J11" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="48" t="s">
+      <c r="K11" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L11" s="48" t="s">
+      <c r="L11" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="M11" s="48" t="s">
+      <c r="M11" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N11" s="48" t="s">
+      <c r="N11" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O11" s="48" t="s">
+      <c r="O11" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q11" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T11" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="V11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X11" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y11" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z11" s="48" t="s">
+      <c r="P11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q11" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T11" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="V11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X11" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y11" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z11" s="41" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="36">
         <v>46106.418981481482</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="39">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="I12" s="44" t="s">
+      <c r="I12" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J12" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K12" s="44" t="s">
+      <c r="K12" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="M12" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N12" s="44" t="s">
+      <c r="N12" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="O12" s="44" t="s">
+      <c r="O12" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P12" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="S12" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="W12" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X12" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y12" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z12" s="44" t="s">
+      <c r="P12" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="S12" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="W12" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y12" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z12" s="37" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
+      <c r="A13" s="40">
         <v>46106.419062499997</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="48" t="s">
+      <c r="H13" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J13" s="48" t="s">
+      <c r="J13" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K13" s="48" t="s">
+      <c r="K13" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L13" s="48" t="s">
+      <c r="L13" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M13" s="48" t="s">
+      <c r="M13" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N13" s="48" t="s">
+      <c r="N13" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O13" s="48" t="s">
+      <c r="O13" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q13" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="U13" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X13" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y13" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z13" s="48" t="s">
+      <c r="P13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="U13" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X13" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y13" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z13" s="41" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="39">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I14" s="44" t="s">
+      <c r="I14" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="J14" s="44" t="s">
+      <c r="J14" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K14" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="44" t="s">
+      <c r="M14" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="N14" s="44" t="s">
+      <c r="N14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O14" s="44" t="s">
+      <c r="O14" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="P14" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q14" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R14" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S14" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="T14" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U14" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="V14" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="W14" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X14" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y14" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z14" s="44" t="s">
+      <c r="P14" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q14" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R14" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S14" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="T14" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U14" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="W14" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X14" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y14" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z14" s="37" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
+      <c r="A15" s="40">
         <v>46106.419988425929</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H15" s="48" t="s">
+      <c r="H15" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J15" s="48" t="s">
+      <c r="J15" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K15" s="48" t="s">
+      <c r="K15" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L15" s="48" t="s">
+      <c r="L15" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M15" s="48" t="s">
+      <c r="M15" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N15" s="48" t="s">
+      <c r="N15" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O15" s="48" t="s">
+      <c r="O15" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q15" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T15" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U15" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X15" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y15" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z15" s="48" t="s">
+      <c r="P15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q15" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T15" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U15" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X15" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y15" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z15" s="41" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="36">
         <v>46106.420046296298</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="39">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="F16" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I16" s="44" t="s">
+      <c r="I16" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J16" s="44" t="s">
+      <c r="J16" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K16" s="44" t="s">
+      <c r="K16" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L16" s="44" t="s">
+      <c r="L16" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M16" s="44" t="s">
+      <c r="M16" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N16" s="44" t="s">
+      <c r="N16" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O16" s="44" t="s">
+      <c r="O16" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q16" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="U16" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V16" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="W16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y16" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z16" s="44" t="s">
+      <c r="P16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q16" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="U16" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V16" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="W16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y16" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z16" s="37" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="47">
+      <c r="A17" s="40">
         <v>46106.420104166667</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="42" t="s">
         <v>242</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="39">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="J17" s="48" t="s">
+      <c r="J17" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L17" s="48" t="s">
+      <c r="L17" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="M17" s="48" t="s">
+      <c r="M17" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N17" s="48" t="s">
+      <c r="N17" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O17" s="48" t="s">
+      <c r="O17" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="S17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="T17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="W17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="X17" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y17" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z17" s="48" t="s">
+      <c r="P17" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="S17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="T17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="W17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="X17" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y17" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z17" s="41" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="A18" s="36">
         <v>46106.420347222222</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G18" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="44" t="s">
+      <c r="I18" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J18" s="44" t="s">
+      <c r="J18" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K18" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L18" s="44" t="s">
+      <c r="L18" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M18" s="44" t="s">
+      <c r="M18" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N18" s="44" t="s">
+      <c r="N18" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O18" s="44" t="s">
+      <c r="O18" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q18" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T18" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U18" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X18" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y18" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z18" s="44" t="s">
+      <c r="P18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q18" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T18" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U18" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X18" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z18" s="37" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="47">
+      <c r="A19" s="40">
         <v>46106.42046296296</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="40" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="39">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I19" s="48" t="s">
+      <c r="I19" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="48" t="s">
+      <c r="J19" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K19" s="48" t="s">
+      <c r="K19" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L19" s="48" t="s">
+      <c r="L19" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M19" s="48" t="s">
+      <c r="M19" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N19" s="48" t="s">
+      <c r="N19" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O19" s="48" t="s">
+      <c r="O19" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P19" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q19" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R19" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="S19" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="T19" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="U19" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V19" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W19" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X19" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y19" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z19" s="48" t="s">
+      <c r="P19" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q19" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R19" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="S19" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="T19" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="U19" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V19" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W19" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X19" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y19" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z19" s="41" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="E20" s="46">
+      <c r="E20" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I20" s="44" t="s">
+      <c r="I20" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J20" s="44" t="s">
+      <c r="J20" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K20" s="44" t="s">
+      <c r="K20" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L20" s="44" t="s">
+      <c r="L20" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M20" s="44" t="s">
+      <c r="M20" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N20" s="44" t="s">
+      <c r="N20" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O20" s="44" t="s">
+      <c r="O20" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q20" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T20" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U20" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X20" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y20" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z20" s="44" t="s">
+      <c r="P20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T20" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U20" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X20" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y20" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z20" s="37" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
+      <c r="A21" s="40">
         <v>46106.421365740738</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="40" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="42" t="s">
         <v>254</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="39">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H21" s="48" t="s">
+      <c r="H21" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I21" s="48" t="s">
+      <c r="I21" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J21" s="48" t="s">
+      <c r="J21" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="K21" s="48" t="s">
+      <c r="K21" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="L21" s="48" t="s">
+      <c r="L21" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M21" s="48" t="s">
+      <c r="M21" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N21" s="48" t="s">
+      <c r="N21" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O21" s="48" t="s">
+      <c r="O21" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q21" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R21" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="S21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="U21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="V21" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="W21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y21" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z21" s="48" t="s">
+      <c r="P21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q21" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R21" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="S21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="U21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="V21" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="W21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y21" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z21" s="41" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+      <c r="A22" s="36">
         <v>46106.422662037039</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="39">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G22" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I22" s="44" t="s">
+      <c r="I22" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="J22" s="44" t="s">
+      <c r="J22" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="L22" s="44" t="s">
+      <c r="L22" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="M22" s="44" t="s">
+      <c r="M22" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N22" s="44" t="s">
+      <c r="N22" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="O22" s="44" t="s">
+      <c r="O22" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q22" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T22" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="V22" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="W22" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="X22" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y22" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z22" s="44" t="s">
+      <c r="P22" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q22" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R22" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S22" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T22" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U22" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V22" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="W22" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="X22" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y22" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z22" s="37" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="47">
+      <c r="A23" s="40">
         <v>46106.42291666667</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F23" s="48" t="s">
+      <c r="F23" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G23" s="48" t="s">
+      <c r="G23" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H23" s="48" t="s">
+      <c r="H23" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I23" s="48" t="s">
+      <c r="I23" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J23" s="48" t="s">
+      <c r="J23" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K23" s="48" t="s">
+      <c r="K23" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L23" s="48" t="s">
+      <c r="L23" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M23" s="48" t="s">
+      <c r="M23" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N23" s="48" t="s">
+      <c r="N23" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O23" s="48" t="s">
+      <c r="O23" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q23" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T23" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U23" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X23" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y23" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z23" s="48" t="s">
+      <c r="P23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q23" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T23" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U23" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X23" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z23" s="41" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="43">
+      <c r="A24" s="36">
         <v>46106.423321759263</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="39">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="F24" s="44" t="s">
+      <c r="F24" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="44" t="s">
+      <c r="G24" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I24" s="44" t="s">
+      <c r="I24" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K24" s="44" t="s">
+      <c r="K24" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="L24" s="44" t="s">
+      <c r="L24" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M24" s="44" t="s">
+      <c r="M24" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N24" s="44" t="s">
+      <c r="N24" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O24" s="44" t="s">
+      <c r="O24" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q24" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="U24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="V24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X24" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y24" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z24" s="44" t="s">
+      <c r="P24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q24" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="U24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X24" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y24" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z24" s="37" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="47">
+      <c r="A25" s="40">
         <v>46106.443576388891</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="39">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G25" s="48" t="s">
+      <c r="G25" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H25" s="48" t="s">
+      <c r="H25" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="I25" s="48" t="s">
+      <c r="I25" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="48" t="s">
+      <c r="J25" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K25" s="48" t="s">
+      <c r="K25" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L25" s="48" t="s">
+      <c r="L25" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M25" s="48" t="s">
+      <c r="M25" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N25" s="48" t="s">
+      <c r="N25" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O25" s="48" t="s">
+      <c r="O25" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P25" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q25" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R25" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S25" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T25" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U25" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V25" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W25" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X25" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y25" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z25" s="48" t="s">
+      <c r="P25" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q25" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T25" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U25" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X25" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y25" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z25" s="41" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
+      <c r="A26" s="36">
         <v>46106.445543981485</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="36" t="s">
         <v>301</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="E26" s="46">
+      <c r="E26" s="39">
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G26" s="44" t="s">
+      <c r="G26" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I26" s="44" t="s">
+      <c r="I26" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J26" s="44" t="s">
+      <c r="J26" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="K26" s="44" t="s">
+      <c r="K26" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L26" s="44" t="s">
+      <c r="L26" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M26" s="44" t="s">
+      <c r="M26" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N26" s="44" t="s">
+      <c r="N26" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O26" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q26" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T26" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U26" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X26" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y26" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z26" s="44" t="s">
+      <c r="P26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q26" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T26" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U26" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X26" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y26" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z26" s="37" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="42" t="s">
         <v>269</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="E27" s="46">
+      <c r="E27" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="48" t="s">
+      <c r="G27" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="H27" s="48" t="s">
+      <c r="H27" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="I27" s="48" t="s">
+      <c r="I27" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="J27" s="48" t="s">
+      <c r="J27" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="K27" s="48" t="s">
+      <c r="K27" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L27" s="48" t="s">
+      <c r="L27" s="41" t="s">
         <v>186</v>
       </c>
-      <c r="M27" s="48" t="s">
+      <c r="M27" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="N27" s="48" t="s">
+      <c r="N27" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="O27" s="48" t="s">
+      <c r="O27" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="P27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q27" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="R27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="S27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="T27" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="U27" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="V27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="W27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="X27" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y27" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z27" s="48" t="s">
+      <c r="P27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q27" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="R27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="S27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="T27" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="U27" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="V27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="W27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="X27" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y27" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z27" s="41" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A28" s="43">
+      <c r="A28" s="36">
         <v>46139.668900462966</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="C28" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="D28" s="51" t="s">
+      <c r="D28" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="E28" s="46">
+      <c r="E28" s="39">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="44" t="s">
+      <c r="G28" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="44" t="s">
+      <c r="I28" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="J28" s="44" t="s">
+      <c r="J28" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="L28" s="44" t="s">
+      <c r="L28" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="M28" s="44" t="s">
+      <c r="M28" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N28" s="44" t="s">
+      <c r="N28" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="O28" s="44" t="s">
+      <c r="O28" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="P28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q28" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="R28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="S28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="T28" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="U28" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="V28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="W28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="X28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y28" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z28" s="44" t="s">
+      <c r="P28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="R28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="S28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="T28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="U28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="V28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="W28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="X28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y28" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z28" s="37" t="s">
         <v>305</v>
       </c>
     </row>
